--- a/jupyter-notebooks/silver/Documentacao_bronze_to_silver.xlsx
+++ b/jupyter-notebooks/silver/Documentacao_bronze_to_silver.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jean\projetos\Hackathon2025-Telco\jupyter-notebooks\silver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DE23E3-E7B4-4129-A5AB-D6F96D4B873D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96272879-A93F-48C6-9656-A2A11B0212AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{01548A7E-1B7A-4C47-A300-BF68119BB3D0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{01548A7E-1B7A-4C47-A300-BF68119BB3D0}"/>
   </bookViews>
   <sheets>
     <sheet name="base_pagamento" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="532">
   <si>
     <t>Nome da Variável</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>DW_NUM_CLIENTE</t>
-  </si>
-  <si>
-    <t>try_cast(DW_NUM_CLIENTE as BIGINT)</t>
   </si>
   <si>
     <t>DW_AREA</t>
@@ -596,15 +593,9 @@
     <t>var_26</t>
   </si>
   <si>
-    <t>try_cast(var_26 as int)</t>
-  </si>
-  <si>
     <t>var_27</t>
   </si>
   <si>
-    <t>try_cast(var_27 as int)</t>
-  </si>
-  <si>
     <t>var_28</t>
   </si>
   <si>
@@ -884,33 +875,18 @@
     <t>var_74</t>
   </si>
   <si>
-    <t>try_cast(var_74 as int)</t>
-  </si>
-  <si>
     <t>var_75</t>
   </si>
   <si>
-    <t>try_cast(var_75 as int)</t>
-  </si>
-  <si>
     <t>var_76</t>
   </si>
   <si>
-    <t>try_cast(var_76 as int)</t>
-  </si>
-  <si>
     <t>var_77</t>
   </si>
   <si>
-    <t>try_cast(var_77 as int)</t>
-  </si>
-  <si>
     <t>var_78</t>
   </si>
   <si>
-    <t>try_cast(var_78 as int)</t>
-  </si>
-  <si>
     <t>var_79</t>
   </si>
   <si>
@@ -932,27 +908,15 @@
     <t>var_82</t>
   </si>
   <si>
-    <t>try_cast(var_82 as int)</t>
-  </si>
-  <si>
     <t>var_83</t>
   </si>
   <si>
-    <t>try_cast(var_83 as int)</t>
-  </si>
-  <si>
     <t>var_84</t>
   </si>
   <si>
-    <t>try_cast(var_84 as int)</t>
-  </si>
-  <si>
     <t>var_85</t>
   </si>
   <si>
-    <t>try_cast(var_85 as int)</t>
-  </si>
-  <si>
     <t>var_86</t>
   </si>
   <si>
@@ -962,43 +926,22 @@
     <t>var_87</t>
   </si>
   <si>
-    <t>try_cast(var_87 as int)</t>
-  </si>
-  <si>
     <t>var_88</t>
   </si>
   <si>
-    <t>try_cast(var_88 as int)</t>
-  </si>
-  <si>
     <t>var_89</t>
   </si>
   <si>
-    <t>try_cast(var_89 as int)</t>
-  </si>
-  <si>
     <t>var_90</t>
   </si>
   <si>
-    <t>try_cast(var_90 as int)</t>
-  </si>
-  <si>
     <t>var_91</t>
   </si>
   <si>
-    <t>try_cast(var_91 as int)</t>
-  </si>
-  <si>
     <t>var_92</t>
   </si>
   <si>
-    <t>try_cast(var_92 as int)</t>
-  </si>
-  <si>
     <t>var_93</t>
-  </si>
-  <si>
-    <t>try_cast(var_93 as int)</t>
   </si>
   <si>
     <r>
@@ -1153,15 +1096,9 @@
     <t>var_18</t>
   </si>
   <si>
-    <t>try_cast(var_18 as int)</t>
-  </si>
-  <si>
     <t>var_19</t>
   </si>
   <si>
-    <t>try_cast(var_19 as int)</t>
-  </si>
-  <si>
     <t>var_20</t>
   </si>
   <si>
@@ -1393,9 +1330,6 @@
     <t>IND_ISENCAO_COB_FAT</t>
   </si>
   <si>
-    <t>try_cast(IND_ISENCAO_COB_FAT as INT)</t>
-  </si>
-  <si>
     <t>IND_WO</t>
   </si>
   <si>
@@ -1528,9 +1462,6 @@
     <t>DW_NUM_NTC</t>
   </si>
   <si>
-    <t>try_cast(DW_NUM_NTC as BIGINT)</t>
-  </si>
-  <si>
     <t>DAT_INSERCAO_CREDITO</t>
   </si>
   <si>
@@ -1679,6 +1610,78 @@
   </si>
   <si>
     <t>TEL</t>
+  </si>
+  <si>
+    <t>try_cast(var_27 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_26 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_74 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_75 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_76 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_77 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_78 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_82 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_83 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_84 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_85 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_87 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_88 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_89 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_90 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_91 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_92 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>try_cast(var_93 as decimal(10,2))</t>
+  </si>
+  <si>
+    <t>Converte para decimal com tratamento de erros retorna null</t>
+  </si>
+  <si>
+    <t>try_cast(var_18 as string)</t>
+  </si>
+  <si>
+    <t>try_cast(var_19 as string)</t>
+  </si>
+  <si>
+    <t>try_cast(DW_NUM_CLIENTE as STRING)</t>
+  </si>
+  <si>
+    <t>try_cast(IND_ISENCAO_COB_FAT as string)</t>
+  </si>
+  <si>
+    <t>try_cast(DW_NUM_NTC as STRING)</t>
   </si>
 </sst>
 </file>
@@ -1727,7 +1730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1755,9 +1758,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2112,7 +2112,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2134,7 +2134,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2145,7 +2145,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2156,7 +2156,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2167,7 +2167,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2178,7 +2178,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2189,7 +2189,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2197,725 +2197,725 @@
         <v>23</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>24</v>
+        <v>529</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>478</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="C12" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="C13" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="C14" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="C17" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="C18" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="C19" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="C20" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="C21" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="C22" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="C23" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>52</v>
-      </c>
       <c r="C24" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="C25" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="C26" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="C27" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="C28" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="C29" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="C30" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>66</v>
-      </c>
       <c r="C31" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="C33" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="C34" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="C35" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>77</v>
-      </c>
       <c r="C36" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="C37" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>81</v>
-      </c>
       <c r="C38" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="C39" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="C40" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="C41" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="C42" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="C43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>93</v>
-      </c>
       <c r="C44" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>95</v>
-      </c>
       <c r="C45" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="C46" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="C47" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="C48" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="C49" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>105</v>
-      </c>
       <c r="C50" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>107</v>
-      </c>
       <c r="C51" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>109</v>
-      </c>
       <c r="C52" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="C53" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="C54" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="C55" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="C56" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>119</v>
-      </c>
       <c r="C57" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="C58" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="C59" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="C60" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>127</v>
-      </c>
       <c r="C61" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="C62" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>131</v>
-      </c>
       <c r="C63" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B64" s="7" t="s">
-        <v>133</v>
-      </c>
       <c r="C64" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B65" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="C65" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>137</v>
-      </c>
       <c r="C66" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="C67" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>141</v>
-      </c>
       <c r="C68" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>143</v>
-      </c>
       <c r="C69" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="C70" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B71" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>147</v>
-      </c>
       <c r="C71" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="C72" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B73" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>151</v>
-      </c>
       <c r="C73" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>153</v>
-      </c>
       <c r="C74" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B75" s="7" t="s">
-        <v>155</v>
-      </c>
       <c r="C75" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="C76" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2954,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2965,40 +2965,40 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3009,29 +3009,29 @@
         <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3039,249 +3039,249 @@
         <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>529</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>478</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="C11" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>435</v>
+        <v>530</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>159</v>
@@ -3289,233 +3289,233 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="C53" s="4" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3554,7 +3554,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3565,40 +3565,40 @@
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>478</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3606,230 +3606,230 @@
         <v>23</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>478</v>
+        <v>529</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="5" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="5" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="5" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="5" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="5" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="5" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="C21" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="5" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="5" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="5" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>157</v>
-      </c>
       <c r="C27" s="8" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3854,31 +3854,31 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="C1" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="D1" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="E1" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="F1" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="G1" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="I1" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="J1" t="s">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="K1" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4542,10 +4542,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4553,813 +4553,813 @@
         <v>6</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>164</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>167</v>
-      </c>
       <c r="C4" s="8" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="C5" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>174</v>
-      </c>
       <c r="C7" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>176</v>
+        <v>509</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>178</v>
+        <v>508</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>272</v>
+        <v>510</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>274</v>
+        <v>511</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>276</v>
+        <v>512</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="5" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>278</v>
+        <v>513</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="5" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>280</v>
+        <v>514</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="5" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="5" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="5" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="5" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>288</v>
+        <v>515</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>290</v>
+        <v>516</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="5" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>292</v>
+        <v>517</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="5" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>294</v>
+        <v>518</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>161</v>
+        <v>526</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="5" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>298</v>
+        <v>519</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="5" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>300</v>
+        <v>520</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="5" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>302</v>
+        <v>521</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="5" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>304</v>
+        <v>522</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="5" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>306</v>
+        <v>523</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="5" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>308</v>
+        <v>524</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="5" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>310</v>
+        <v>525</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>159</v>
+        <v>526</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>157</v>
-      </c>
       <c r="C76" s="8" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -5393,10 +5393,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5404,260 +5404,260 @@
         <v>6</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>167</v>
-      </c>
       <c r="C4" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="C5" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>171</v>
-      </c>
       <c r="C6" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>174</v>
-      </c>
       <c r="C7" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="5" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="5" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="5" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="5" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="5" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="5" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="5" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="5" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="5" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="5" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>355</v>
+        <v>527</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>159</v>
@@ -5665,10 +5665,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="5" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>357</v>
+        <v>528</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>159</v>
@@ -5676,90 +5676,90 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="5" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="5" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="5" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="5" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="5" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>157</v>
-      </c>
       <c r="C35" s="8" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -5793,10 +5793,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5804,87 +5804,87 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>380</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
